--- a/ASMR_table.xlsx
+++ b/ASMR_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univpm-my.sharepoint.com/personal/s1116344_pm_univpm_it/Documents/PhD/ASMR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2624" documentId="8_{924902AC-4CEC-4633-955D-BBD51FD90869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{276E6FF2-554D-4ED2-9300-4F7ACB1C8DAD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EA71B3-D007-486B-AF3A-124BA8F8001F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{4BFF25AA-47A3-4D4C-BB08-0C4994EE28E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{4BFF25AA-47A3-4D4C-BB08-0C4994EE28E5}"/>
   </bookViews>
   <sheets>
     <sheet name="location (2)" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Bo_et_al_2011!$A$1:$Q$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">metadata_term_list!$A$1:$P$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">metadata_term_list!$A$1:$O$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="859">
   <si>
     <t>coordinatePrecision</t>
   </si>
@@ -2465,9 +2465,6 @@
     <t xml:space="preserve">This 2 miles elongated pinnacle (41°06.45′N–10°54.43′E, summit of the peak), represents the survey area. Here the bedrock takes the form of ridges separated by joints of various size and extent, traced by sandy sediments and running north eastward [19]. </t>
   </si>
   <si>
-    <t>FILL</t>
-  </si>
-  <si>
     <t>Marine Ecoregions of the World, MEOW (Spalding et al., 2007)</t>
   </si>
   <si>
@@ -2615,9 +2612,6 @@
     <t>REPORTED</t>
   </si>
   <si>
-    <t>Abstract</t>
-  </si>
-  <si>
     <t>Introduction</t>
   </si>
   <si>
@@ -2696,9 +2690,6 @@
     <t>Contextual information: ecological</t>
   </si>
   <si>
-    <t>Even if not strictly the focus of the study, provide a brief description of the habitat/biocoenosis and substrate type, possibly referring to standard classifications.</t>
-  </si>
-  <si>
     <t>eco: excludedHabitatScope</t>
   </si>
   <si>
@@ -2706,9 +2697,6 @@
   </si>
   <si>
     <t>asmr:substrateClassification</t>
-  </si>
-  <si>
-    <t>Contextual information: conservation</t>
   </si>
   <si>
     <t>If relevant to the study, specify the overall conservation status of the site (if available citing assessments) and mention relevant pressure to which it is or has been subjected.</t>
@@ -3101,24 +3089,6 @@
     <t>Biotic parameters</t>
   </si>
   <si>
-    <t>Jacobsen</t>
-  </si>
-  <si>
-    <t>t.pulido@staff.univpm.it</t>
-  </si>
-  <si>
-    <t>Università Politecnica delle Marche, Ancona, Italy</t>
-  </si>
-  <si>
-    <t>National Recovery and Resilience Plan (NRRP), Mission 4 Component 2 Investment 1.4—Call for tender No. 3138 of 16 December 2021, rectified by Decree n.3175 of 18 December 2021 of the Italian Ministry for Universities and Research funded by the European Union—NextGenerationEU; Project code CN_00000033, Concession Decree No. 1034 of 17 June 2022 adopted by the Italian Ministry for Universities and Research, CUP I33C22001300007, Project title ‘National Biodiversity Future Center (NBFC)’ | Interreg Med MPA Engage ‘Engaging Mediterranean key actors in Ecosystem Approach to manage Marine Protected Areas to face Climate change’ (grant number 5216)</t>
-  </si>
-  <si>
-    <t>https://creativecommons.org/licenses/by/4.0/</t>
-  </si>
-  <si>
-    <t>Jacobsen, N., Roveta, C., Pulido Mantas, T., Coppari, M., Di Camillo, C., Calcinai, B. and Cerrano, C. (2024), Assessment of Octocoral-Dominated Benthic Assemblages Along a Mesophotic Gradient, With a Focus on the Impact of Lost Fishing Gears. Aquatic Conserv: Mar Freshw Ecosyst, 34: e4248. https://doi.org/10.1002/aqc.4248</t>
-  </si>
-  <si>
     <t>sessile | vagile</t>
   </si>
   <si>
@@ -3141,6 +3111,51 @@
   </si>
   <si>
     <t>Depth range should de expressed in m below the sea level (m).  If depth  is given with an error, include, consider it (e.g. if transects were carried at 35±3, then the mininum depth is 32 m and maximum is 38 m).</t>
+  </si>
+  <si>
+    <t>Even if not strictly the focus of the study, provide a brief description of the habitat and substrate type, possibly referring to standard classifications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contextual information: conservation </t>
+  </si>
+  <si>
+    <t>The Vercelli Seamount is not heavily exploited by professional fishing. Nevertheless, some abandoned nets and lines were observed along the ROV track. Environments characterised by high biodiversity should be worthy of protection by international conservation programs.</t>
+  </si>
+  <si>
+    <t>Mandatory if asmr:ecoregionName and asmr:ecoregionName are specified.</t>
+  </si>
+  <si>
+    <t>asmr:restrictedLithology</t>
+  </si>
+  <si>
+    <t>hard, soft, consolidated sediment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISGM Seabed geomorphology - Physiography Vocabulary https://pid.geoscience.gov.au/def/voc/ga/SeabedGeomorphologyPhysiography </t>
+  </si>
+  <si>
+    <t>continental slope
+continental rise
+abyssal plain
+accretionary prism
+axial high
+axial valley
+back-arc basin
+continental shelf
+fore-arc basin
+island arc
+mid-ocean ridge
+oceanic trench
++ hadal</t>
+  </si>
+  <si>
+    <t>asmr:physiographicContext</t>
+  </si>
+  <si>
+    <t>Physiographical features as defined by the  ISGM Physiography vocabulary</t>
+  </si>
+  <si>
+    <t>asmr:ecologicalParameters</t>
   </si>
 </sst>
 </file>
@@ -3434,7 +3449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3585,17 +3600,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4246,7 +4255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F13874E-1C67-4C5D-801F-ACA3BCCD8AD8}">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" style="11" customWidth="1"/>
@@ -4259,12 +4268,12 @@
     <col min="8" max="8" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
+        <v>702</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>703</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>704</v>
       </c>
       <c r="C1" s="39" t="s">
         <v>6</v>
@@ -4273,1337 +4282,1327 @@
         <v>8</v>
       </c>
       <c r="E1" s="39" t="s">
+        <v>704</v>
+      </c>
+      <c r="F1" s="39" t="s">
         <v>705</v>
       </c>
-      <c r="F1" s="39" t="s">
-        <v>706</v>
-      </c>
-      <c r="G1" s="52" t="s">
-        <v>818</v>
-      </c>
-      <c r="H1" s="45" t="s">
-        <v>825</v>
+      <c r="G1" s="39" t="s">
+        <v>814</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="B2" s="41" t="s">
         <v>707</v>
       </c>
-      <c r="B2" s="41"/>
       <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="D2" s="41" t="s">
+        <v>708</v>
+      </c>
       <c r="E2" s="41"/>
       <c r="F2" s="41"/>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
-        <v>708</v>
-      </c>
-      <c r="B3" s="41" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="55"/>
+      <c r="B3" s="55" t="s">
         <v>709</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41" t="s">
-        <v>710</v>
-      </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" s="55"/>
+      <c r="G3" s="54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="57"/>
-      <c r="B4" s="57" t="s">
-        <v>711</v>
-      </c>
+      <c r="B4" s="57"/>
       <c r="C4" s="57"/>
       <c r="D4" s="57"/>
       <c r="E4" s="42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F4" s="57"/>
-      <c r="G4" s="56" t="b">
+      <c r="G4" s="54"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="42" t="s">
+        <v>710</v>
+      </c>
+      <c r="F5" s="57"/>
+      <c r="G5" s="54"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="41" t="s">
+        <v>711</v>
+      </c>
+      <c r="F6" s="56"/>
+      <c r="G6" s="54"/>
+    </row>
+    <row r="7" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="40"/>
+      <c r="B7" s="41" t="s">
+        <v>712</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="51" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F5" s="59"/>
-      <c r="G5" s="56"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="42" t="s">
-        <v>712</v>
-      </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="56"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="41" t="s">
+    </row>
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="43" t="s">
         <v>713</v>
       </c>
-      <c r="F7" s="58"/>
-      <c r="G7" s="56"/>
-    </row>
-    <row r="8" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="40"/>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="55" t="s">
+        <v>715</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>716</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>708</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="F8" s="55"/>
+      <c r="G8" s="54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="43" t="s">
         <v>714</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="51" t="b">
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="54"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="48"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="41" t="s">
+        <v>717</v>
+      </c>
+      <c r="F10" s="56"/>
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" spans="1:10" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>719</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>708</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="55"/>
+      <c r="G11" s="54" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="44" t="s">
+        <v>720</v>
+      </c>
+      <c r="F13" s="56"/>
+      <c r="G13" s="54"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="55"/>
+      <c r="B14" s="45" t="s">
+        <v>721</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>723</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>708</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" s="55"/>
+      <c r="G14" s="54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
-        <v>715</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>717</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>718</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>710</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
-        <v>716</v>
-      </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="56"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="48"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="41" t="s">
-        <v>719</v>
-      </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="56"/>
-    </row>
-    <row r="12" spans="1:10" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57" t="s">
-        <v>720</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>721</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>710</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="56" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="56"/>
-    </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="44" t="s">
-        <v>722</v>
-      </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="56"/>
-    </row>
-    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="57"/>
       <c r="B15" s="45" t="s">
-        <v>723</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>725</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>710</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="57"/>
       <c r="E15" s="45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F15" s="57"/>
-      <c r="G15" s="56" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
-      <c r="B16" s="45" t="s">
+      <c r="G15" s="54"/>
+    </row>
+    <row r="16" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="45" t="s">
         <v>724</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="56"/>
-    </row>
-    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="59"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="57"/>
+      <c r="G16" s="54"/>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="57"/>
       <c r="B17" s="49"/>
       <c r="C17" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="D17" s="57"/>
+      <c r="E17" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="54"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="57"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="45" t="s">
         <v>726</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="56"/>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="45" t="s">
-        <v>727</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="F18" s="59"/>
-      <c r="G18" s="56"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
-      <c r="D19" s="59"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="56"/>
+        <v>727</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
+      <c r="A20" s="57"/>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
-      <c r="D20" s="59"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="F20" s="59"/>
-      <c r="G20" s="56"/>
+        <v>728</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>
-      <c r="D21" s="59"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="45" t="s">
+        <v>729</v>
+      </c>
+      <c r="F21" s="57"/>
+      <c r="G21" s="54"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="56"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="41" t="s">
         <v>730</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="56"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="45" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="55"/>
+      <c r="B23" s="55" t="s">
         <v>731</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="56"/>
-    </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="58"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="41" t="s">
+      <c r="C23" s="55" t="s">
+        <v>848</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="F23" s="58"/>
-      <c r="G23" s="56"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="57"/>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="57"/>
+      <c r="G24" s="54"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="57"/>
+      <c r="G25" s="54"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="45" t="s">
         <v>733</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="F27" s="57"/>
+      <c r="G27" s="54"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="45" t="s">
         <v>734</v>
       </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="42" t="s">
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="56"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="56"/>
+      <c r="G29" s="54"/>
+    </row>
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="55"/>
+      <c r="B30" s="55" t="s">
+        <v>849</v>
+      </c>
+      <c r="C30" s="45" t="s">
         <v>735</v>
       </c>
-      <c r="F24" s="57"/>
-      <c r="G24" s="56" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="59"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="56"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="56"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="45" t="s">
+      <c r="D30" s="55"/>
+      <c r="E30" s="45" t="s">
+        <v>737</v>
+      </c>
+      <c r="F30" s="55"/>
+      <c r="G30" s="54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="56"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="41" t="s">
         <v>736</v>
       </c>
-      <c r="F27" s="59"/>
-      <c r="G27" s="56"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="59"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="F28" s="59"/>
-      <c r="G28" s="56"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="59"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="45" t="s">
-        <v>737</v>
-      </c>
-      <c r="F29" s="59"/>
-      <c r="G29" s="56"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="F30" s="58"/>
-      <c r="G30" s="56"/>
-    </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="57" t="s">
+      <c r="D31" s="56"/>
+      <c r="E31" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" s="56"/>
+      <c r="G31" s="54"/>
+    </row>
+    <row r="32" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41" t="s">
         <v>738</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="C32" s="41" t="s">
         <v>739</v>
       </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="45" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="55"/>
+      <c r="B33" s="55" t="s">
+        <v>740</v>
+      </c>
+      <c r="C33" s="55" t="s">
         <v>741</v>
       </c>
-      <c r="F31" s="57"/>
-      <c r="G31" s="56" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="41" t="s">
-        <v>740</v>
-      </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="58"/>
-      <c r="G32" s="56"/>
-    </row>
-    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="40"/>
-      <c r="B33" s="41" t="s">
+      <c r="D33" s="55"/>
+      <c r="E33" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="F33" s="55"/>
+      <c r="G33" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="56"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="44" t="s">
         <v>742</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="F34" s="56"/>
+      <c r="G34" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41" t="s">
         <v>743</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="57"/>
-      <c r="B34" s="57" t="s">
+      <c r="C35" s="41" t="s">
         <v>744</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="D35" s="41"/>
+      <c r="E35" s="41" t="s">
         <v>745</v>
       </c>
-      <c r="D34" s="57"/>
-      <c r="E34" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F34" s="57"/>
-      <c r="G34" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="44" t="s">
-        <v>746</v>
-      </c>
-      <c r="F35" s="58"/>
-      <c r="G35" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F35" s="41"/>
+      <c r="G35" s="52" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="40"/>
       <c r="B36" s="41" t="s">
+        <v>746</v>
+      </c>
+      <c r="C36" s="41" t="s">
         <v>747</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="D36" s="41"/>
+      <c r="E36" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="F36" s="41"/>
+      <c r="G36" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="55"/>
+      <c r="B37" s="55" t="s">
         <v>748</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41" t="s">
+      <c r="C37" s="55" t="s">
         <v>749</v>
       </c>
-      <c r="F36" s="41"/>
-      <c r="G36" s="53" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41" t="s">
+      <c r="D37" s="55"/>
+      <c r="E37" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="F37" s="55"/>
+      <c r="G37" s="51" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="56"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="55"/>
+      <c r="B39" s="55" t="s">
         <v>750</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C39" s="45" t="s">
         <v>751</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="57"/>
-      <c r="B38" s="57" t="s">
-        <v>752</v>
-      </c>
-      <c r="C38" s="57" t="s">
-        <v>753</v>
-      </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="42" t="s">
-        <v>510</v>
-      </c>
-      <c r="F38" s="57"/>
-      <c r="G38" s="51" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="58"/>
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="F39" s="58"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="55"/>
+      <c r="G39" s="51" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="57"/>
-      <c r="B40" s="57" t="s">
-        <v>754</v>
-      </c>
+      <c r="B40" s="57"/>
       <c r="C40" s="45" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D40" s="57"/>
       <c r="E40" s="42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F40" s="57"/>
       <c r="G40" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
-      <c r="B41" s="59"/>
+        <v>817</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
       <c r="C41" s="45" t="s">
-        <v>756</v>
-      </c>
-      <c r="D41" s="59"/>
+        <v>753</v>
+      </c>
+      <c r="D41" s="57"/>
       <c r="E41" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="F41" s="59"/>
+        <v>415</v>
+      </c>
+      <c r="F41" s="57"/>
       <c r="G41" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="59"/>
-      <c r="B42" s="59"/>
-      <c r="C42" s="45" t="s">
-        <v>757</v>
-      </c>
-      <c r="D42" s="59"/>
-      <c r="E42" s="42" t="s">
-        <v>415</v>
-      </c>
-      <c r="F42" s="59"/>
-      <c r="G42" s="51" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="44" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="F43" s="58"/>
-    </row>
-    <row r="44" spans="1:7" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="56"/>
+    </row>
+    <row r="43" spans="1:7" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="55"/>
+      <c r="B43" s="55" t="s">
+        <v>754</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>816</v>
+      </c>
+      <c r="D43" s="55"/>
+      <c r="E43" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="55"/>
+      <c r="G43" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="57"/>
-      <c r="B44" s="57" t="s">
-        <v>758</v>
-      </c>
-      <c r="C44" s="57" t="s">
-        <v>820</v>
-      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
       <c r="D44" s="57"/>
       <c r="E44" s="42" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F44" s="57"/>
       <c r="G44" s="51" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
-      <c r="B45" s="59"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
       <c r="E45" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="F45" s="59"/>
+        <v>246</v>
+      </c>
+      <c r="F45" s="57"/>
       <c r="G45" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="59"/>
-      <c r="B46" s="59"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="F46" s="59"/>
+        <v>817</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="F46" s="56"/>
       <c r="G46" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="58"/>
+        <v>817</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="40"/>
+      <c r="B47" s="41" t="s">
+        <v>755</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>756</v>
+      </c>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
       <c r="G47" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="40"/>
-      <c r="B48" s="41" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="55"/>
+      <c r="B48" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>758</v>
+      </c>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="41" t="s">
         <v>759</v>
       </c>
-      <c r="C48" s="41" t="s">
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="55"/>
+      <c r="B50" s="55" t="s">
         <v>760</v>
       </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="57"/>
-      <c r="B49" s="57" t="s">
+      <c r="C50" s="55" t="s">
         <v>761</v>
       </c>
-      <c r="C49" s="45" t="s">
+      <c r="D50" s="55"/>
+      <c r="E50" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="F50" s="55"/>
+      <c r="G50" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+    </row>
+    <row r="52" spans="1:7" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="55"/>
+      <c r="B52" s="55" t="s">
         <v>762</v>
       </c>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="41" t="s">
+      <c r="C52" s="55" t="s">
         <v>763</v>
       </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57" t="s">
-        <v>764</v>
-      </c>
-      <c r="C51" s="57" t="s">
-        <v>765</v>
-      </c>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="F51" s="57"/>
-      <c r="G51" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-    </row>
-    <row r="53" spans="1:7" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="55"/>
+      <c r="E52" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="F52" s="55"/>
+      <c r="G52" s="54" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="57"/>
-      <c r="B53" s="57" t="s">
-        <v>766</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>767</v>
-      </c>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
       <c r="D53" s="57"/>
       <c r="E53" s="45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F53" s="57"/>
-      <c r="G53" s="56" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="59"/>
-      <c r="B54" s="59"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="F54" s="59"/>
-      <c r="G54" s="56"/>
-    </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="56"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="57"/>
-      <c r="B56" s="57" t="s">
+      <c r="G53" s="54"/>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="54"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="55"/>
+      <c r="B55" s="55" t="s">
         <v>254</v>
       </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="45" t="s">
+      <c r="C55" s="55"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="F56" s="57"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="F56" s="56"/>
       <c r="G56" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="58"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="F57" s="58"/>
-      <c r="G57" s="51" t="s">
-        <v>822</v>
-      </c>
+        <v>818</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="40" t="s">
+        <v>764</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>765</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>766</v>
+      </c>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
     </row>
     <row r="58" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="40" t="s">
+      <c r="A58" s="40"/>
+      <c r="B58" s="41" t="s">
+        <v>767</v>
+      </c>
+      <c r="C58" s="41" t="s">
         <v>768</v>
-      </c>
-      <c r="B58" s="41" t="s">
-        <v>769</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>770</v>
       </c>
       <c r="D58" s="41"/>
       <c r="E58" s="41"/>
       <c r="F58" s="41"/>
     </row>
-    <row r="59" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="40"/>
+    <row r="59" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="40" t="s">
+        <v>769</v>
+      </c>
       <c r="B59" s="41" t="s">
+        <v>770</v>
+      </c>
+      <c r="C59" s="41" t="s">
         <v>771</v>
-      </c>
-      <c r="C59" s="41" t="s">
-        <v>772</v>
       </c>
       <c r="D59" s="41"/>
       <c r="E59" s="41"/>
       <c r="F59" s="41"/>
-    </row>
-    <row r="60" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="40" t="s">
+      <c r="G59" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="40"/>
+      <c r="B60" s="41" t="s">
+        <v>772</v>
+      </c>
+      <c r="C60" s="41" t="s">
         <v>773</v>
-      </c>
-      <c r="B60" s="41" t="s">
-        <v>774</v>
-      </c>
-      <c r="C60" s="41" t="s">
-        <v>775</v>
       </c>
       <c r="D60" s="41"/>
       <c r="E60" s="41"/>
       <c r="F60" s="41"/>
       <c r="G60" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="40"/>
-      <c r="B61" s="41" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="55"/>
+      <c r="B61" s="55" t="s">
+        <v>774</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>775</v>
+      </c>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55" t="s">
         <v>776</v>
       </c>
-      <c r="C61" s="41" t="s">
+      <c r="F61" s="55"/>
+      <c r="G61" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="56"/>
+      <c r="B62" s="56"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="55"/>
+      <c r="B63" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="45" t="s">
         <v>777</v>
       </c>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="51" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="258.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="57"/>
-      <c r="B62" s="57" t="s">
+      <c r="D63" s="55"/>
+      <c r="E63" s="45" t="s">
+        <v>779</v>
+      </c>
+      <c r="F63" s="55"/>
+      <c r="G63" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="57"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="45" t="s">
         <v>778</v>
-      </c>
-      <c r="C62" s="57" t="s">
-        <v>779</v>
-      </c>
-      <c r="D62" s="57"/>
-      <c r="E62" s="57" t="s">
-        <v>780</v>
-      </c>
-      <c r="F62" s="57"/>
-      <c r="G62" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="58"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="57"/>
-      <c r="B64" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C64" s="45" t="s">
-        <v>781</v>
       </c>
       <c r="D64" s="57"/>
       <c r="E64" s="45" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F64" s="57"/>
       <c r="G64" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="59"/>
-      <c r="B65" s="59"/>
-      <c r="C65" s="45" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="57"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="45" t="s">
+        <v>781</v>
+      </c>
+      <c r="F65" s="57"/>
+      <c r="G65" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="57"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="45" t="s">
         <v>782</v>
       </c>
-      <c r="D65" s="59"/>
-      <c r="E65" s="45" t="s">
+      <c r="F66" s="57"/>
+      <c r="G66" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="41" t="s">
+        <v>783</v>
+      </c>
+      <c r="F67" s="56"/>
+      <c r="G67" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="40" t="s">
         <v>784</v>
       </c>
-      <c r="F65" s="59"/>
-      <c r="G65" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="59"/>
-      <c r="B66" s="59"/>
-      <c r="C66" s="49"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="45" t="s">
+      <c r="B68" s="41" t="s">
         <v>785</v>
       </c>
-      <c r="F66" s="59"/>
-      <c r="G66" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="59"/>
-      <c r="B67" s="59"/>
-      <c r="C67" s="49"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="45" t="s">
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="40"/>
+      <c r="B69" s="41" t="s">
         <v>786</v>
       </c>
-      <c r="F67" s="59"/>
-      <c r="G67" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="41" t="s">
+      <c r="C69" s="41" t="s">
         <v>787</v>
       </c>
-      <c r="F68" s="58"/>
-      <c r="G68" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="40" t="s">
-        <v>788</v>
-      </c>
-      <c r="B69" s="41" t="s">
-        <v>789</v>
-      </c>
-      <c r="C69" s="41"/>
       <c r="D69" s="41"/>
       <c r="E69" s="41"/>
       <c r="F69" s="41"/>
       <c r="G69" s="51" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="40"/>
       <c r="B70" s="41" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D70" s="41"/>
       <c r="E70" s="41"/>
       <c r="F70" s="41"/>
       <c r="G70" s="51" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="40"/>
       <c r="B71" s="41" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C71" s="41" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D71" s="41"/>
       <c r="E71" s="41"/>
       <c r="F71" s="41"/>
       <c r="G71" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="40"/>
-      <c r="B72" s="41" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="55"/>
+      <c r="B72" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" s="45" t="s">
+        <v>792</v>
+      </c>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="56"/>
+      <c r="B73" s="56"/>
+      <c r="C73" s="41" t="s">
+        <v>793</v>
+      </c>
+      <c r="D73" s="56"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="40"/>
+      <c r="B74" s="41" t="s">
         <v>794</v>
       </c>
-      <c r="C72" s="41" t="s">
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="55"/>
+      <c r="B75" s="55" t="s">
         <v>795</v>
       </c>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C73" s="45" t="s">
+      <c r="C75" s="45" t="s">
         <v>796</v>
       </c>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="58"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="41" t="s">
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="56"/>
+      <c r="B76" s="56"/>
+      <c r="C76" s="41" t="s">
         <v>797</v>
       </c>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="40"/>
-      <c r="B75" s="41" t="s">
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="40"/>
+      <c r="B77" s="41" t="s">
         <v>798</v>
       </c>
-      <c r="C75" s="41"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="57" t="s">
+      <c r="C77" s="47" t="s">
         <v>799</v>
       </c>
-      <c r="C76" s="45" t="s">
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="51" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="40" t="s">
         <v>800</v>
       </c>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="58"/>
-      <c r="B77" s="58"/>
-      <c r="C77" s="41" t="s">
+      <c r="B78" s="41" t="s">
         <v>801</v>
       </c>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58"/>
-      <c r="G77" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="40"/>
-      <c r="B78" s="41" t="s">
+      <c r="C78" s="41" t="s">
         <v>802</v>
-      </c>
-      <c r="C78" s="47" t="s">
-        <v>803</v>
       </c>
       <c r="D78" s="41"/>
       <c r="E78" s="41"/>
       <c r="F78" s="41"/>
       <c r="G78" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="40" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="40"/>
+      <c r="B79" s="41" t="s">
+        <v>803</v>
+      </c>
+      <c r="C79" s="41" t="s">
         <v>804</v>
-      </c>
-      <c r="B79" s="41" t="s">
-        <v>805</v>
-      </c>
-      <c r="C79" s="41" t="s">
-        <v>806</v>
       </c>
       <c r="D79" s="41"/>
       <c r="E79" s="41"/>
       <c r="F79" s="41"/>
       <c r="G79" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="40"/>
-      <c r="B80" s="41" t="s">
-        <v>807</v>
-      </c>
-      <c r="C80" s="41" t="s">
-        <v>808</v>
-      </c>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="51" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="55"/>
+      <c r="B80" s="55" t="s">
+        <v>805</v>
+      </c>
+      <c r="C80" s="45" t="s">
+        <v>806</v>
+      </c>
+      <c r="D80" s="55"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="55"/>
+      <c r="G80" s="54" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="57"/>
-      <c r="B81" s="57" t="s">
-        <v>809</v>
-      </c>
-      <c r="C81" s="45" t="s">
-        <v>810</v>
-      </c>
+      <c r="B81" s="57"/>
+      <c r="C81" s="46"/>
       <c r="D81" s="57"/>
       <c r="E81" s="57"/>
       <c r="F81" s="57"/>
-      <c r="G81" s="56" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="59"/>
-      <c r="B82" s="59"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="56"/>
-    </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="41" t="s">
+      <c r="G81" s="54"/>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="56"/>
+      <c r="B82" s="56"/>
+      <c r="C82" s="41" t="s">
+        <v>807</v>
+      </c>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="54"/>
+    </row>
+    <row r="83" spans="1:7" ht="330.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="55"/>
+      <c r="B83" s="55" t="s">
+        <v>808</v>
+      </c>
+      <c r="C83" s="55" t="s">
+        <v>809</v>
+      </c>
+      <c r="D83" s="55"/>
+      <c r="E83" s="55"/>
+      <c r="F83" s="55"/>
+      <c r="G83" s="54" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="56"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="56"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="54"/>
+    </row>
+    <row r="85" spans="1:7" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="55"/>
+      <c r="B85" s="55" t="s">
+        <v>810</v>
+      </c>
+      <c r="C85" s="55" t="s">
         <v>811</v>
       </c>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="56"/>
-    </row>
-    <row r="84" spans="1:7" ht="330.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="57"/>
-      <c r="B84" s="57" t="s">
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="54" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="54"/>
+    </row>
+    <row r="87" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="40"/>
+      <c r="B87" s="41" t="s">
         <v>812</v>
       </c>
-      <c r="C84" s="57" t="s">
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41" t="s">
         <v>813</v>
       </c>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="56" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="56"/>
-    </row>
-    <row r="86" spans="1:7" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="57"/>
-      <c r="B86" s="57" t="s">
-        <v>814</v>
-      </c>
-      <c r="C86" s="57" t="s">
-        <v>815</v>
-      </c>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="56" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="58"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="56"/>
-    </row>
-    <row r="88" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="40"/>
-      <c r="B88" s="41" t="s">
-        <v>816</v>
-      </c>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41" t="s">
-        <v>817</v>
-      </c>
-      <c r="G88" s="51" t="s">
-        <v>822</v>
+      <c r="G87" s="51" t="s">
+        <v>818</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="A15:A23"/>
-    <mergeCell ref="D15:D23"/>
-    <mergeCell ref="F15:F23"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="B24:B30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="D24:D30"/>
-    <mergeCell ref="F24:F30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="D64:D68"/>
-    <mergeCell ref="F64:F68"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="E81:E83"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G23"/>
-    <mergeCell ref="G24:G30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="D14:D22"/>
+    <mergeCell ref="F14:F22"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="C23:C29"/>
+    <mergeCell ref="D23:D29"/>
+    <mergeCell ref="F23:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="F63:F67"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="G14:G22"/>
+    <mergeCell ref="G23:G29"/>
+    <mergeCell ref="G30:G31"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" location="eco_geospatialScopeAreaUnit" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaUnit" xr:uid="{80841094-9A0D-4D37-806C-878EB6061EA8}"/>
-    <hyperlink ref="E5" r:id="rId2" location="eco_geospatialScopeAreaValue" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaValue" xr:uid="{62E41486-0BA9-4A18-AF6B-C298883B3B54}"/>
-    <hyperlink ref="E6" r:id="rId3" location="eco_targetHabitatScope" display="https://eco.tdwg.org/list/ - eco_targetHabitatScope" xr:uid="{89FBFBA0-E983-4DCA-A64C-1E3C1A8098B2}"/>
-    <hyperlink ref="E9" r:id="rId4" location="eco_eventDurationUnit" display="https://eco.tdwg.org/list/ - eco_eventDurationUnit" xr:uid="{E48EC115-084C-4BB1-9752-8D33D3ABB77F}"/>
-    <hyperlink ref="E10" r:id="rId5" location="eco_eventDurationValue" display="https://eco.tdwg.org/list/ - eco_eventDurationValue" xr:uid="{80991C3C-D34D-445C-92CC-95723AF1FBD4}"/>
-    <hyperlink ref="E12" r:id="rId6" location="dwc_projectID" display="https://dwc.tdwg.org/list/ - dwc_projectID" xr:uid="{2909D5DF-8EB8-4015-B20C-43FB64F6B319}"/>
-    <hyperlink ref="E13" r:id="rId7" location="dwc_projectTitle" display="https://dwc.tdwg.org/list/ - dwc_projectTitle" xr:uid="{69318421-CEE1-4D18-B478-CA7B8F42DB7B}"/>
-    <hyperlink ref="E14" r:id="rId8" location="eco_samplingPerformedBy" display="https://eco.tdwg.org/list/ - eco_samplingPerformedBy" xr:uid="{48EF5B0E-A117-468F-B57C-EB38CEC0E182}"/>
-    <hyperlink ref="E17" r:id="rId9" location="eco_totalAreaSampledUnit" display="https://eco.tdwg.org/list/ - eco_totalAreaSampledUnit" xr:uid="{CEF5077A-7C5A-414E-A3B3-3F714ECC96BA}"/>
-    <hyperlink ref="E18" r:id="rId10" location="eco_totalAreaSampledValue" display="https://eco.tdwg.org/list/ - eco_totalAreaSampledValue" xr:uid="{3CE7EE2A-1B0C-4B9A-949C-010EA65CF6C7}"/>
-    <hyperlink ref="E24" r:id="rId11" location="eco_excludedHabitatScope" display="https://eco.tdwg.org/list/ - eco_excludedHabitatScope" xr:uid="{A075FDDB-165F-4DC9-B596-6DD69FEA1C3D}"/>
-    <hyperlink ref="E34" r:id="rId12" location="eco_reportedWeather" display="https://eco.tdwg.org/list/ - eco_reportedWeather" xr:uid="{DC7CF1D5-B5AF-4988-9948-E29583D91823}"/>
-    <hyperlink ref="E35" r:id="rId13" location="eco_reportedExtremeConditions" display="https://eco.tdwg.org/list/ - eco_reportedExtremeConditions" xr:uid="{A59DE4EF-DBD7-43EC-A3B0-A92A21CAEA8B}"/>
-    <hyperlink ref="E37" r:id="rId14" location="eco_protocolDescriptions" display="https://eco.tdwg.org/list/ - eco_protocolDescriptions" xr:uid="{2328F4A3-B26C-4B74-B26B-A0826EBDB19D}"/>
-    <hyperlink ref="E38" r:id="rId15" location="eco_protocolNames" display="https://eco.tdwg.org/list/ - eco_protocolNames" xr:uid="{567BB9BD-A3F0-4C2D-92EB-0BC90FD996B2}"/>
-    <hyperlink ref="E39" r:id="rId16" location="eco_protocolReferences" display="https://eco.tdwg.org/list/ - eco_protocolReferences" xr:uid="{AA758BA0-3E5B-4180-A602-1FC3F801E9B9}"/>
-    <hyperlink ref="E40" r:id="rId17" location="eco_siteCount" display="https://eco.tdwg.org/list/ - eco_siteCount" xr:uid="{5540EF3E-F758-488A-89C1-DFBC60C32352}"/>
-    <hyperlink ref="E41" r:id="rId18" location="eco_siteNestingDescription" display="https://eco.tdwg.org/list/ - eco_siteNestingDescription" xr:uid="{6CFD0FFE-8506-457B-9A8C-1992CD1EC90A}"/>
-    <hyperlink ref="E42" r:id="rId19" location="eco_verbatimSiteDescriptions" display="https://eco.tdwg.org/list/ - eco_verbatimSiteDescriptions" xr:uid="{230C23B1-13C5-47F4-A98C-8A6104E531EB}"/>
-    <hyperlink ref="E43" r:id="rId20" location="eco_verbatimSiteNames" display="https://eco.tdwg.org/list/ - eco_verbatimSiteNames" xr:uid="{EACC519E-61A2-4114-8AC3-12F5EE0D4363}"/>
-    <hyperlink ref="E44" r:id="rId21" location="eco_isSamplingEffortReported" display="https://eco.tdwg.org/list/ - eco_isSamplingEffortReported" xr:uid="{15EECC44-C4CB-4464-B3EE-01BB67D93BD4}"/>
-    <hyperlink ref="E45" r:id="rId22" location="eco_samplingEffortValue" display="https://eco.tdwg.org/list/ - eco_samplingEffortValue" xr:uid="{D8C57448-63F4-4ED8-B663-E7D2844494E2}"/>
-    <hyperlink ref="E46" r:id="rId23" location="eco_samplingEffortUnit" display="https://eco.tdwg.org/list/ - eco_samplingEffortUnit" xr:uid="{76CDA717-DBDE-445C-8650-D9DB0E13854F}"/>
-    <hyperlink ref="E47" r:id="rId24" location="eco_samplingEffortProtocol" display="https://eco.tdwg.org/list/ - eco_samplingEffortProtocol" xr:uid="{7DF6606F-7899-451A-A1E8-D00F8A5E7858}"/>
+    <hyperlink ref="E3" r:id="rId1" location="eco_geospatialScopeAreaUnit" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaUnit" xr:uid="{80841094-9A0D-4D37-806C-878EB6061EA8}"/>
+    <hyperlink ref="E4" r:id="rId2" location="eco_geospatialScopeAreaValue" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaValue" xr:uid="{62E41486-0BA9-4A18-AF6B-C298883B3B54}"/>
+    <hyperlink ref="E5" r:id="rId3" location="eco_targetHabitatScope" display="https://eco.tdwg.org/list/ - eco_targetHabitatScope" xr:uid="{89FBFBA0-E983-4DCA-A64C-1E3C1A8098B2}"/>
+    <hyperlink ref="E8" r:id="rId4" location="eco_eventDurationUnit" display="https://eco.tdwg.org/list/ - eco_eventDurationUnit" xr:uid="{E48EC115-084C-4BB1-9752-8D33D3ABB77F}"/>
+    <hyperlink ref="E9" r:id="rId5" location="eco_eventDurationValue" display="https://eco.tdwg.org/list/ - eco_eventDurationValue" xr:uid="{80991C3C-D34D-445C-92CC-95723AF1FBD4}"/>
+    <hyperlink ref="E11" r:id="rId6" location="dwc_projectID" display="https://dwc.tdwg.org/list/ - dwc_projectID" xr:uid="{2909D5DF-8EB8-4015-B20C-43FB64F6B319}"/>
+    <hyperlink ref="E12" r:id="rId7" location="dwc_projectTitle" display="https://dwc.tdwg.org/list/ - dwc_projectTitle" xr:uid="{69318421-CEE1-4D18-B478-CA7B8F42DB7B}"/>
+    <hyperlink ref="E13" r:id="rId8" location="eco_samplingPerformedBy" display="https://eco.tdwg.org/list/ - eco_samplingPerformedBy" xr:uid="{48EF5B0E-A117-468F-B57C-EB38CEC0E182}"/>
+    <hyperlink ref="E16" r:id="rId9" location="eco_totalAreaSampledUnit" display="https://eco.tdwg.org/list/ - eco_totalAreaSampledUnit" xr:uid="{CEF5077A-7C5A-414E-A3B3-3F714ECC96BA}"/>
+    <hyperlink ref="E17" r:id="rId10" location="eco_totalAreaSampledValue" display="https://eco.tdwg.org/list/ - eco_totalAreaSampledValue" xr:uid="{3CE7EE2A-1B0C-4B9A-949C-010EA65CF6C7}"/>
+    <hyperlink ref="E23" r:id="rId11" location="eco_excludedHabitatScope" display="https://eco.tdwg.org/list/ - eco_excludedHabitatScope" xr:uid="{A075FDDB-165F-4DC9-B596-6DD69FEA1C3D}"/>
+    <hyperlink ref="E33" r:id="rId12" location="eco_reportedWeather" display="https://eco.tdwg.org/list/ - eco_reportedWeather" xr:uid="{DC7CF1D5-B5AF-4988-9948-E29583D91823}"/>
+    <hyperlink ref="E34" r:id="rId13" location="eco_reportedExtremeConditions" display="https://eco.tdwg.org/list/ - eco_reportedExtremeConditions" xr:uid="{A59DE4EF-DBD7-43EC-A3B0-A92A21CAEA8B}"/>
+    <hyperlink ref="E36" r:id="rId14" location="eco_protocolDescriptions" display="https://eco.tdwg.org/list/ - eco_protocolDescriptions" xr:uid="{2328F4A3-B26C-4B74-B26B-A0826EBDB19D}"/>
+    <hyperlink ref="E37" r:id="rId15" location="eco_protocolNames" display="https://eco.tdwg.org/list/ - eco_protocolNames" xr:uid="{567BB9BD-A3F0-4C2D-92EB-0BC90FD996B2}"/>
+    <hyperlink ref="E38" r:id="rId16" location="eco_protocolReferences" display="https://eco.tdwg.org/list/ - eco_protocolReferences" xr:uid="{AA758BA0-3E5B-4180-A602-1FC3F801E9B9}"/>
+    <hyperlink ref="E39" r:id="rId17" location="eco_siteCount" display="https://eco.tdwg.org/list/ - eco_siteCount" xr:uid="{5540EF3E-F758-488A-89C1-DFBC60C32352}"/>
+    <hyperlink ref="E40" r:id="rId18" location="eco_siteNestingDescription" display="https://eco.tdwg.org/list/ - eco_siteNestingDescription" xr:uid="{6CFD0FFE-8506-457B-9A8C-1992CD1EC90A}"/>
+    <hyperlink ref="E41" r:id="rId19" location="eco_verbatimSiteDescriptions" display="https://eco.tdwg.org/list/ - eco_verbatimSiteDescriptions" xr:uid="{230C23B1-13C5-47F4-A98C-8A6104E531EB}"/>
+    <hyperlink ref="E42" r:id="rId20" location="eco_verbatimSiteNames" display="https://eco.tdwg.org/list/ - eco_verbatimSiteNames" xr:uid="{EACC519E-61A2-4114-8AC3-12F5EE0D4363}"/>
+    <hyperlink ref="E43" r:id="rId21" location="eco_isSamplingEffortReported" display="https://eco.tdwg.org/list/ - eco_isSamplingEffortReported" xr:uid="{15EECC44-C4CB-4464-B3EE-01BB67D93BD4}"/>
+    <hyperlink ref="E44" r:id="rId22" location="eco_samplingEffortValue" display="https://eco.tdwg.org/list/ - eco_samplingEffortValue" xr:uid="{D8C57448-63F4-4ED8-B663-E7D2844494E2}"/>
+    <hyperlink ref="E45" r:id="rId23" location="eco_samplingEffortUnit" display="https://eco.tdwg.org/list/ - eco_samplingEffortUnit" xr:uid="{76CDA717-DBDE-445C-8650-D9DB0E13854F}"/>
+    <hyperlink ref="E46" r:id="rId24" location="eco_samplingEffortProtocol" display="https://eco.tdwg.org/list/ - eco_samplingEffortProtocol" xr:uid="{7DF6606F-7899-451A-A1E8-D00F8A5E7858}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5611,7 +5610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374CAC2C-1632-4DD5-8D59-2134E770C16C}">
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:O164"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="11" customWidth="1"/>
@@ -5629,10 +5628,9 @@
     <col min="13" max="13" width="24.6640625" style="11" customWidth="1"/>
     <col min="14" max="14" width="61.6640625" style="11" customWidth="1"/>
     <col min="15" max="15" width="28.109375" style="11" customWidth="1"/>
-    <col min="16" max="16" width="140" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>48</v>
       </c>
@@ -5678,11 +5676,8 @@
       <c r="O1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>61</v>
       </c>
@@ -5713,11 +5708,8 @@
       <c r="O2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>61</v>
       </c>
@@ -5748,11 +5740,8 @@
       <c r="O3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="16" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>61</v>
       </c>
@@ -5778,11 +5767,8 @@
         <v>160</v>
       </c>
       <c r="N4" s="6"/>
-      <c r="P4" s="29" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>61</v>
       </c>
@@ -5810,11 +5796,8 @@
       <c r="N5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>61</v>
       </c>
@@ -5842,11 +5825,8 @@
       <c r="N6" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>61</v>
       </c>
@@ -5875,7 +5855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>61</v>
       </c>
@@ -5902,7 +5882,7 @@
       </c>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>61</v>
       </c>
@@ -5930,11 +5910,8 @@
       <c r="N9" s="16" t="s">
         <v>635</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>61</v>
       </c>
@@ -5963,7 +5940,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>61</v>
       </c>
@@ -5992,7 +5969,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>61</v>
       </c>
@@ -6021,7 +5998,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>61</v>
       </c>
@@ -6052,11 +6029,8 @@
       <c r="O13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>61</v>
       </c>
@@ -6087,11 +6061,8 @@
       <c r="N14" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>61</v>
       </c>
@@ -6123,7 +6094,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>61</v>
       </c>
@@ -6149,9 +6120,6 @@
         <v>114</v>
       </c>
       <c r="N16" s="6"/>
-      <c r="P16" s="1" t="s">
-        <v>616</v>
-      </c>
     </row>
     <row r="17" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
@@ -6437,6 +6405,9 @@
       <c r="D26" s="6" t="s">
         <v>288</v>
       </c>
+      <c r="E26" s="6" t="s">
+        <v>851</v>
+      </c>
       <c r="F26" s="14" t="s">
         <v>68</v>
       </c>
@@ -6458,6 +6429,9 @@
       <c r="D27" s="6" t="s">
         <v>291</v>
       </c>
+      <c r="E27" s="6" t="s">
+        <v>679</v>
+      </c>
       <c r="F27" s="14" t="s">
         <v>68</v>
       </c>
@@ -6482,6 +6456,9 @@
       <c r="D28" s="6" t="s">
         <v>290</v>
       </c>
+      <c r="E28" s="6" t="s">
+        <v>679</v>
+      </c>
       <c r="F28" s="14" t="s">
         <v>68</v>
       </c>
@@ -6503,7 +6480,7 @@
       <c r="C29" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>256</v>
       </c>
       <c r="F29" s="14" t="s">
@@ -6545,7 +6522,7 @@
         <v>162</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -6557,99 +6534,98 @@
       </c>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>64</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="F32" s="14"/>
       <c r="M32" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B33" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>676</v>
-      </c>
-      <c r="F33" s="14"/>
-      <c r="K33" s="6" t="s">
-        <v>317</v>
+        <v>169</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="144" x14ac:dyDescent="0.3">
       <c r="B34" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>293</v>
+        <v>675</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="K34" s="6" t="s">
+        <v>317</v>
       </c>
       <c r="M34" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B35" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>171</v>
+        <v>856</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>285</v>
+        <v>857</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>64</v>
+        <v>88</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>293</v>
       </c>
       <c r="M35" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="N35" s="6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>82</v>
@@ -6657,9 +6633,6 @@
       <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K36" s="16" t="s">
-        <v>287</v>
-      </c>
       <c r="M36" s="11" t="s">
         <v>220</v>
       </c>
@@ -6667,45 +6640,44 @@
         <v>605</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B37" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>680</v>
+        <v>286</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>319</v>
+      <c r="K37" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="M37" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="N37" s="6"/>
-    </row>
-    <row r="38" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>232</v>
-      </c>
+      <c r="N37" s="6" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B38" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>318</v>
+        <v>681</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>679</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>68</v>
@@ -6713,38 +6685,38 @@
       <c r="H38" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>322</v>
-      </c>
       <c r="L38" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M38" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>232</v>
+      </c>
       <c r="B39" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>84</v>
+        <v>64</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M39" s="11" t="s">
         <v>220</v>
@@ -6756,58 +6728,61 @@
         <v>162</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>294</v>
+        <v>680</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>679</v>
       </c>
       <c r="F40" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>321</v>
       </c>
       <c r="M40" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B41" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>324</v>
+        <v>191</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>679</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>680</v>
+        <v>294</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>323</v>
+        <v>64</v>
       </c>
       <c r="M41" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="144" x14ac:dyDescent="0.3">
       <c r="B42" s="17" t="s">
         <v>162</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>325</v>
+        <v>678</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>679</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>68</v>
@@ -6815,55 +6790,47 @@
       <c r="H42" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>326</v>
+      <c r="K42" s="6" t="s">
+        <v>323</v>
       </c>
       <c r="M42" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:15" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B43" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>186</v>
+        <v>162</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>192</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>143</v>
+        <v>325</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>145</v>
+        <v>326</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="O43" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:15" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="17" t="s">
         <v>163</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>365</v>
+        <v>143</v>
       </c>
       <c r="F44" s="14" t="s">
         <v>63</v>
@@ -6872,89 +6839,92 @@
         <v>88</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N44" s="25" t="s">
-        <v>151</v>
+        <v>146</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="17" t="s">
         <v>163</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>427</v>
+        <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>429</v>
+        <v>365</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J45" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="L45" s="6" t="s">
-        <v>430</v>
+        <v>149</v>
       </c>
       <c r="M45" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="B46" s="17" t="s">
         <v>163</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>188</v>
+        <v>427</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>152</v>
+        <v>428</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="F46" s="14" t="s">
         <v>82</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="J46" s="6"/>
       <c r="L46" s="6" t="s">
-        <v>153</v>
+        <v>430</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="N46" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="N46" s="25" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B47" s="17" t="s">
         <v>163</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>82</v>
@@ -6963,79 +6933,82 @@
         <v>64</v>
       </c>
       <c r="L47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B48" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M48" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="N47" s="6"/>
-    </row>
-    <row r="48" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B48" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="M48" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N48" s="25" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B49" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F49" s="14"/>
       <c r="M49" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>531</v>
+        <v>218</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>64</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="F50" s="14"/>
       <c r="M50" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N50" s="25" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7043,78 +7016,80 @@
         <v>233</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>362</v>
+        <v>531</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="F51" s="19" t="s">
         <v>82</v>
       </c>
+      <c r="H51" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="M51" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N51" s="6"/>
+        <v>150</v>
+      </c>
+      <c r="N51" s="25" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="52" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B52" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>64</v>
+        <v>363</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>82</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N52" s="25" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B53" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>374</v>
+        <v>261</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>68</v>
+        <v>426</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N53" s="6"/>
-    </row>
-    <row r="54" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="N53" s="25" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>375</v>
@@ -7130,92 +7105,84 @@
       </c>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="2:14" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B55" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>431</v>
+        <v>238</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>432</v>
+        <v>373</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="F55" s="14"/>
+        <v>375</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="M55" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N55" s="25" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="2:14" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F56" s="14"/>
       <c r="M56" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N56" s="25" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" ht="291.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B57" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>440</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="F57" s="14"/>
       <c r="M57" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N57" s="25" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="291.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F58" s="14" t="s">
         <v>82</v>
@@ -7226,11 +7193,14 @@
       <c r="J58" s="11" t="s">
         <v>263</v>
       </c>
+      <c r="L58" s="6" t="s">
+        <v>440</v>
+      </c>
       <c r="M58" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N58" s="25" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7238,34 +7208,39 @@
         <v>233</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>851</v>
+        <v>449</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>853</v>
+        <v>443</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="F59" s="14" t="s">
         <v>82</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>88</v>
+        <v>444</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="N59" s="25"/>
+        <v>263</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="N59" s="25" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="60" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B60" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>513</v>
@@ -7273,116 +7248,114 @@
       <c r="F60" s="14" t="s">
         <v>82</v>
       </c>
+      <c r="H60" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>840</v>
+      </c>
       <c r="N60" s="25"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B61" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>445</v>
+        <v>842</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>844</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="F61" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="F61" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="H61" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="M61" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N61" s="25" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="N61" s="25"/>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B62" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>64</v>
+        <v>444</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M62" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N62" s="25" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" ht="144" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B63" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="M63" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N63" s="25" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" ht="129.6" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="144" x14ac:dyDescent="0.3">
       <c r="B64" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>64</v>
+        <v>444</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M64" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N64" s="25" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
@@ -7390,57 +7363,54 @@
         <v>233</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="M65" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N65" s="25" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B66" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>473</v>
+        <v>444</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M66" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N66" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -7448,10 +7418,10 @@
         <v>233</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>472</v>
@@ -7459,25 +7429,31 @@
       <c r="F67" s="11" t="s">
         <v>82</v>
       </c>
+      <c r="H67" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>473</v>
+      </c>
       <c r="M67" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N67" s="25" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B68" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>82</v>
@@ -7486,36 +7462,30 @@
         <v>150</v>
       </c>
       <c r="N68" s="25" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B69" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="H69" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L69" s="6" t="s">
-        <v>479</v>
-      </c>
       <c r="M69" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N69" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
@@ -7523,10 +7493,10 @@
         <v>233</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>478</v>
@@ -7544,59 +7514,65 @@
         <v>150</v>
       </c>
       <c r="N70" s="25" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B71" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>630</v>
+        <v>465</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>263</v>
+        <v>64</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>479</v>
       </c>
       <c r="M71" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N71" s="25" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B72" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>466</v>
+        <v>630</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>82</v>
       </c>
+      <c r="H72" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>263</v>
+      </c>
       <c r="M72" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -7604,10 +7580,10 @@
         <v>233</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>484</v>
@@ -7619,50 +7595,44 @@
         <v>150</v>
       </c>
       <c r="N73" s="25" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B74" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="H74" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>263</v>
-      </c>
       <c r="M74" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N74" s="25" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>82</v>
@@ -7677,60 +7647,62 @@
         <v>150</v>
       </c>
       <c r="N75" s="25" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="23" t="s">
         <v>233</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M76" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N76" s="25" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B77" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="N77" s="25" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B77" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>701</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="M77" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N77" s="6"/>
-    </row>
-    <row r="78" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
         <v>161</v>
       </c>
@@ -7738,26 +7710,26 @@
         <v>255</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>85</v>
+        <v>194</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>349</v>
+        <v>84</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>837</v>
       </c>
       <c r="M78" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>161</v>
       </c>
@@ -7765,29 +7737,26 @@
         <v>255</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>591</v>
+        <v>354</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>64</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M79" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>161</v>
       </c>
@@ -7795,19 +7764,22 @@
         <v>255</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="F80" s="14" t="s">
-        <v>82</v>
+        <v>346</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>591</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>64</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="M80" s="11" t="s">
         <v>220</v>
@@ -7815,60 +7787,57 @@
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>161</v>
+      </c>
       <c r="B81" s="20" t="s">
         <v>255</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>603</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="F81" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="F81" s="14" t="s">
         <v>82</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>601</v>
+        <v>313</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="N81" s="6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
-        <v>161</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B82" s="20" t="s">
         <v>255</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>589</v>
+        <v>603</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>82</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>312</v>
+        <v>601</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N82" s="6"/>
+        <v>602</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="83" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
@@ -7878,10 +7847,10 @@
         <v>255</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>202</v>
@@ -7891,6 +7860,9 @@
       </c>
       <c r="H83" s="6" t="s">
         <v>64</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="M83" s="11" t="s">
         <v>220</v>
@@ -7905,10 +7877,10 @@
         <v>255</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>202</v>
@@ -7918,9 +7890,6 @@
       </c>
       <c r="H84" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="M84" s="11" t="s">
         <v>220</v>
@@ -7935,10 +7904,10 @@
         <v>255</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>604</v>
+        <v>197</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>202</v>
@@ -7947,14 +7916,17 @@
         <v>589</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>87</v>
+        <v>64</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>311</v>
       </c>
       <c r="M85" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N85" s="6"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
         <v>161</v>
       </c>
@@ -7962,23 +7934,26 @@
         <v>255</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>199</v>
+        <v>604</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F86" s="14" t="s">
-        <v>82</v>
+        <v>309</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>589</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M86" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N86" s="6"/>
     </row>
-    <row r="87" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
         <v>161</v>
       </c>
@@ -7986,13 +7961,10 @@
         <v>255</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>701</v>
+        <v>308</v>
       </c>
       <c r="F87" s="14" t="s">
         <v>82</v>
@@ -8000,18 +7972,12 @@
       <c r="H87" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K87" s="16" t="s">
-        <v>700</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>702</v>
-      </c>
       <c r="M87" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N87" s="6"/>
     </row>
-    <row r="88" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
         <v>161</v>
       </c>
@@ -8019,10 +7985,13 @@
         <v>255</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>295</v>
+        <v>307</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>700</v>
       </c>
       <c r="F88" s="14" t="s">
         <v>82</v>
@@ -8030,12 +7999,18 @@
       <c r="H88" s="6" t="s">
         <v>64</v>
       </c>
+      <c r="K88" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>701</v>
+      </c>
       <c r="M88" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>161</v>
       </c>
@@ -8043,26 +8018,23 @@
         <v>255</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>202</v>
+        <v>295</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>297</v>
+        <v>64</v>
       </c>
       <c r="M89" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
         <v>161</v>
       </c>
@@ -8070,29 +8042,26 @@
         <v>255</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>590</v>
-      </c>
       <c r="H90" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L90" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="M90" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:14" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>161</v>
       </c>
@@ -8100,10 +8069,10 @@
         <v>255</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>202</v>
@@ -8112,17 +8081,17 @@
         <v>590</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L91" s="6">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="L91" s="21" t="s">
+        <v>300</v>
       </c>
       <c r="M91" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
         <v>161</v>
       </c>
@@ -8130,25 +8099,22 @@
         <v>255</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>202</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>502</v>
+        <v>590</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="L92" s="6" t="b">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="L92" s="6">
+        <v>1</v>
       </c>
       <c r="M92" s="11" t="s">
         <v>220</v>
@@ -8163,23 +8129,32 @@
         <v>255</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>202</v>
       </c>
+      <c r="G93" s="6" t="s">
+        <v>502</v>
+      </c>
       <c r="H93" s="6" t="s">
-        <v>64</v>
+        <v>259</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="L93" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="M93" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N93" s="6"/>
     </row>
-    <row r="94" spans="1:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
         <v>161</v>
       </c>
@@ -8187,17 +8162,14 @@
         <v>255</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>502</v>
-      </c>
       <c r="H94" s="6" t="s">
         <v>64</v>
       </c>
@@ -8206,7 +8178,7 @@
       </c>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
         <v>161</v>
       </c>
@@ -8214,10 +8186,10 @@
         <v>255</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>202</v>
@@ -8241,10 +8213,10 @@
         <v>255</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>202</v>
@@ -8260,31 +8232,34 @@
       </c>
       <c r="N96" s="6"/>
     </row>
-    <row r="97" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B97" s="26" t="s">
-        <v>211</v>
+      <c r="B97" s="20" t="s">
+        <v>255</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>663</v>
+        <v>210</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>502</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>665</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>664</v>
+        <v>64</v>
       </c>
       <c r="M97" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:16" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
         <v>161</v>
       </c>
@@ -8292,31 +8267,23 @@
         <v>211</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>500</v>
+        <v>662</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>663</v>
       </c>
       <c r="M98" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N98" s="25" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:15" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
         <v>161</v>
       </c>
@@ -8324,34 +8291,31 @@
         <v>211</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="L99" s="7" t="s">
-        <v>505</v>
+        <v>501</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>500</v>
       </c>
       <c r="M99" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N99" s="25" t="s">
-        <v>553</v>
-      </c>
-      <c r="O99" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
         <v>161</v>
       </c>
@@ -8359,31 +8323,34 @@
         <v>211</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>505</v>
       </c>
       <c r="M100" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N100" s="25" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+      <c r="O100" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
         <v>161</v>
       </c>
@@ -8391,34 +8358,31 @@
         <v>211</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="H101" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>263</v>
+      <c r="G101" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>509</v>
       </c>
       <c r="M101" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N101" s="25" t="s">
-        <v>555</v>
-      </c>
-      <c r="P101" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
         <v>161</v>
       </c>
@@ -8426,13 +8390,13 @@
         <v>211</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>82</v>
@@ -8447,10 +8411,10 @@
         <v>150</v>
       </c>
       <c r="N102" s="25" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
         <v>161</v>
       </c>
@@ -8458,25 +8422,31 @@
         <v>211</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>517</v>
       </c>
       <c r="F103" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>87</v>
+        <v>259</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M103" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N103" s="25" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
         <v>161</v>
       </c>
@@ -8484,45 +8454,42 @@
         <v>211</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="M104" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N104" s="25" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C105" s="22" t="s">
-        <v>248</v>
+      <c r="C105" s="13" t="s">
+        <v>519</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>262</v>
+        <v>520</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>521</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>259</v>
@@ -8534,36 +8501,39 @@
         <v>150</v>
       </c>
       <c r="N105" s="25" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C106" s="13" t="s">
-        <v>247</v>
+      <c r="C106" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>366</v>
+        <v>262</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>63</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>87</v>
+        <v>259</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M106" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N106" s="25" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
         <v>161</v>
       </c>
@@ -8571,32 +8541,25 @@
         <v>211</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H107" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K107" s="7"/>
-      <c r="L107" s="6" t="s">
-        <v>260</v>
+      <c r="H107" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="M107" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N107" s="25" t="s">
-        <v>568</v>
-      </c>
-      <c r="O107" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
         <v>161</v>
       </c>
@@ -8604,25 +8567,32 @@
         <v>211</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>264</v>
+        <v>367</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H108" s="6" t="s">
-        <v>64</v>
+      <c r="H108" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K108" s="7"/>
+      <c r="L108" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="M108" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N108" s="25" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+      <c r="O108" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
         <v>161</v>
       </c>
@@ -8630,23 +8600,25 @@
         <v>211</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F109" s="14" t="s">
-        <v>82</v>
+        <v>264</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>64</v>
       </c>
       <c r="M109" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N109" s="6"/>
-    </row>
-    <row r="110" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="N109" s="25" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
         <v>161</v>
       </c>
@@ -8654,10 +8626,10 @@
         <v>211</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F110" s="14" t="s">
         <v>82</v>
@@ -8670,7 +8642,7 @@
       </c>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>161</v>
       </c>
@@ -8678,29 +8650,23 @@
         <v>211</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>510</v>
+        <v>251</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H111" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F111" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H111" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K111" s="7"/>
       <c r="M111" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N111" s="25" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
         <v>161</v>
       </c>
@@ -8708,28 +8674,29 @@
         <v>211</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>235</v>
+        <v>510</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>266</v>
+        <v>511</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="F112" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H112" s="6" t="s">
+      <c r="H112" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="K112" s="7"/>
       <c r="M112" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N112" s="25" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
         <v>161</v>
       </c>
@@ -8737,16 +8704,16 @@
         <v>211</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="F113" s="14" t="s">
-        <v>82</v>
+        <v>512</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>64</v>
@@ -8755,10 +8722,10 @@
         <v>150</v>
       </c>
       <c r="N113" s="25" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
         <v>161</v>
       </c>
@@ -8766,10 +8733,13 @@
         <v>211</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>513</v>
       </c>
       <c r="F114" s="14" t="s">
         <v>82</v>
@@ -8777,15 +8747,14 @@
       <c r="H114" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L114" s="6" t="s">
-        <v>269</v>
-      </c>
       <c r="M114" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N114" s="6"/>
-    </row>
-    <row r="115" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="N114" s="25" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
         <v>161</v>
       </c>
@@ -8793,25 +8762,26 @@
         <v>211</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>63</v>
+        <v>268</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>87</v>
+        <v>64</v>
+      </c>
+      <c r="L115" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="M115" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N115" s="25" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
         <v>161</v>
       </c>
@@ -8819,28 +8789,25 @@
         <v>211</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>649</v>
+        <v>270</v>
       </c>
       <c r="F116" s="11" t="s">
         <v>63</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M116" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N116" s="25" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
         <v>161</v>
       </c>
@@ -8848,10 +8815,13 @@
         <v>211</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>271</v>
+        <v>648</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>649</v>
       </c>
       <c r="F117" s="11" t="s">
         <v>63</v>
@@ -8863,10 +8833,10 @@
         <v>150</v>
       </c>
       <c r="N117" s="25" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
         <v>161</v>
       </c>
@@ -8874,10 +8844,10 @@
         <v>211</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>63</v>
@@ -8889,60 +8859,60 @@
         <v>150</v>
       </c>
       <c r="N118" s="25" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B119" s="23" t="s">
-        <v>233</v>
+      <c r="B119" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>441</v>
+        <v>230</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="F119" s="14"/>
+        <v>272</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="M119" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N119" s="25" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B120" s="26" t="s">
-        <v>211</v>
+      <c r="B120" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>275</v>
+        <v>441</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>279</v>
+        <v>628</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>82</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="F120" s="14"/>
       <c r="M120" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N120" s="25" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
         <v>161</v>
       </c>
@@ -8950,13 +8920,13 @@
         <v>211</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>82</v>
@@ -8965,10 +8935,10 @@
         <v>150</v>
       </c>
       <c r="N121" s="25" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>161</v>
       </c>
@@ -8976,23 +8946,25 @@
         <v>211</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>356</v>
+        <v>280</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>423</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="H122" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="M122" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N122" s="6"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="N122" s="25" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
         <v>161</v>
       </c>
@@ -9000,20 +8972,23 @@
         <v>211</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>82</v>
       </c>
+      <c r="H123" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="M123" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>161</v>
       </c>
@@ -9021,23 +8996,20 @@
         <v>211</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>368</v>
+        <v>277</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="H124" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="M124" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>161</v>
       </c>
@@ -9045,10 +9017,10 @@
         <v>211</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F125" s="11" t="s">
         <v>82</v>
@@ -9061,7 +9033,7 @@
       </c>
       <c r="N125" s="6"/>
     </row>
-    <row r="126" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
         <v>161</v>
       </c>
@@ -9069,26 +9041,21 @@
         <v>211</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>231</v>
+        <v>369</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>63</v>
+        <v>371</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M126" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N126" s="25" t="s">
-        <v>566</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N126" s="6"/>
     </row>
     <row r="127" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
@@ -9098,10 +9065,13 @@
         <v>211</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="F127" s="14" t="s">
         <v>63</v>
@@ -9109,17 +9079,14 @@
       <c r="H127" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="6" t="s">
-        <v>284</v>
-      </c>
       <c r="M127" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N127" s="25" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
         <v>161</v>
       </c>
@@ -9127,24 +9094,26 @@
         <v>211</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>85</v>
+        <v>283</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="M128" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N128" s="6"/>
+        <v>150</v>
+      </c>
+      <c r="N128" s="25" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
@@ -9154,13 +9123,13 @@
         <v>211</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>239</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>259</v>
@@ -9173,7 +9142,7 @@
       </c>
       <c r="N129" s="6"/>
     </row>
-    <row r="130" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>161</v>
       </c>
@@ -9181,20 +9150,26 @@
         <v>211</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>359</v>
+        <v>225</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="F130" s="19" t="s">
-        <v>85</v>
+        <v>239</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="L130" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="M130" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N130" s="6"/>
     </row>
-    <row r="131" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
         <v>161</v>
       </c>
@@ -9202,19 +9177,13 @@
         <v>211</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>241</v>
+        <v>359</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>87</v>
+        <v>360</v>
+      </c>
+      <c r="F131" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="M131" s="11" t="s">
         <v>220</v>
@@ -9229,13 +9198,13 @@
         <v>211</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="F132" s="14" t="s">
         <v>63</v>
@@ -9256,13 +9225,16 @@
         <v>211</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F133" s="19" t="s">
-        <v>85</v>
+        <v>338</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>87</v>
@@ -9280,10 +9252,10 @@
         <v>211</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F134" s="19" t="s">
         <v>85</v>
@@ -9304,16 +9276,13 @@
         <v>211</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F135" s="11" t="s">
-        <v>82</v>
+        <v>343</v>
+      </c>
+      <c r="F135" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>87</v>
@@ -9331,10 +9300,13 @@
         <v>211</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>376</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>82</v>
@@ -9347,7 +9319,7 @@
       </c>
       <c r="N136" s="6"/>
     </row>
-    <row r="137" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
         <v>161</v>
       </c>
@@ -9355,52 +9327,52 @@
         <v>211</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>587</v>
+        <v>345</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>87</v>
       </c>
       <c r="M137" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="N137" s="16" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B138" s="27" t="s">
-        <v>254</v>
+      <c r="B138" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>336</v>
+        <v>586</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>587</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N138" s="6"/>
-    </row>
-    <row r="139" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="N138" s="16" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
         <v>161</v>
       </c>
@@ -9408,10 +9380,10 @@
         <v>254</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>82</v>
@@ -9424,34 +9396,31 @@
       </c>
       <c r="N139" s="6"/>
     </row>
-    <row r="140" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B140" s="28" t="s">
-        <v>214</v>
+      <c r="B140" s="27" t="s">
+        <v>254</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L140" s="6">
-        <v>1056</v>
+        <v>64</v>
       </c>
       <c r="M140" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N140" s="6"/>
     </row>
-    <row r="141" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
         <v>161</v>
       </c>
@@ -9459,26 +9428,26 @@
         <v>214</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L141" s="6">
-        <v>11</v>
+        <v>1056</v>
       </c>
       <c r="M141" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N141" s="6"/>
     </row>
-    <row r="142" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>161</v>
       </c>
@@ -9486,26 +9455,26 @@
         <v>214</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L142" s="6" t="s">
-        <v>327</v>
+        <v>84</v>
+      </c>
+      <c r="L142" s="6">
+        <v>11</v>
       </c>
       <c r="M142" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N142" s="6"/>
     </row>
-    <row r="143" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>161</v>
       </c>
@@ -9513,23 +9482,26 @@
         <v>214</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>87</v>
+        <v>64</v>
+      </c>
+      <c r="L143" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="M143" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
         <v>161</v>
       </c>
@@ -9537,10 +9509,10 @@
         <v>214</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>82</v>
@@ -9553,36 +9525,31 @@
       </c>
       <c r="N144" s="6"/>
     </row>
-    <row r="145" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="C145" s="30" t="s">
-        <v>574</v>
+        <v>161</v>
+      </c>
+      <c r="B145" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>329</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="F145" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H145" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J145" s="11" t="s">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="M145" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="N145" s="25" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
         <v>115</v>
       </c>
@@ -9590,22 +9557,28 @@
         <v>571</v>
       </c>
       <c r="C146" s="30" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>578</v>
+        <v>572</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="J146" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="M146" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N146" s="25" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
         <v>115</v>
       </c>
@@ -9613,19 +9586,22 @@
         <v>571</v>
       </c>
       <c r="C147" s="30" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="M147" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N147" s="25" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="11" t="s">
         <v>115</v>
       </c>
@@ -9633,70 +9609,73 @@
         <v>571</v>
       </c>
       <c r="C148" s="30" t="s">
-        <v>581</v>
+        <v>580</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="M148" s="11" t="s">
         <v>150</v>
       </c>
       <c r="N148" s="25" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A149" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="C149" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="M149" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="N149" s="25" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B149" s="17" t="s">
+    <row r="150" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B150" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C150" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D150" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F149" s="14" t="s">
+      <c r="F150" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H149" s="6" t="s">
+      <c r="H150" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="L149" s="6" t="s">
+      <c r="L150" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M149" s="11" t="s">
+      <c r="M150" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="N149" s="6"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B150" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="C150" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="F150" s="14"/>
-      <c r="M150" s="11" t="s">
-        <v>602</v>
-      </c>
       <c r="N150" s="6"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A151" s="11" t="s">
-        <v>115</v>
-      </c>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B151" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="C151" s="30" t="s">
-        <v>594</v>
-      </c>
+      <c r="C151" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="F151" s="14"/>
       <c r="M151" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="N151" s="6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>115</v>
       </c>
@@ -9704,7 +9683,7 @@
         <v>570</v>
       </c>
       <c r="C152" s="30" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M152" s="11" t="s">
         <v>602</v>
@@ -9713,7 +9692,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="153" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
         <v>115</v>
       </c>
@@ -9721,10 +9700,7 @@
         <v>570</v>
       </c>
       <c r="C153" s="30" t="s">
-        <v>596</v>
-      </c>
-      <c r="H153" s="6" t="s">
-        <v>84</v>
+        <v>595</v>
       </c>
       <c r="M153" s="11" t="s">
         <v>602</v>
@@ -9733,7 +9709,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
         <v>115</v>
       </c>
@@ -9741,7 +9717,10 @@
         <v>570</v>
       </c>
       <c r="C154" s="30" t="s">
-        <v>597</v>
+        <v>596</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="M154" s="11" t="s">
         <v>602</v>
@@ -9750,7 +9729,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
         <v>115</v>
       </c>
@@ -9758,7 +9737,7 @@
         <v>570</v>
       </c>
       <c r="C155" s="30" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="M155" s="11" t="s">
         <v>602</v>
@@ -9767,7 +9746,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>115</v>
       </c>
@@ -9775,13 +9754,7 @@
         <v>570</v>
       </c>
       <c r="C156" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>64</v>
+        <v>598</v>
       </c>
       <c r="M156" s="11" t="s">
         <v>602</v>
@@ -9790,7 +9763,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
         <v>115</v>
       </c>
@@ -9798,7 +9771,13 @@
         <v>570</v>
       </c>
       <c r="C157" s="30" t="s">
-        <v>600</v>
+        <v>599</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="M157" s="11" t="s">
         <v>602</v>
@@ -9807,81 +9786,70 @@
         <v>605</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="37" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A158" s="31" t="s">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B158" s="32" t="s">
+      <c r="B158" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="C158" s="30" t="s">
+        <v>600</v>
+      </c>
+      <c r="M158" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="N158" s="6" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" s="37" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A159" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="C158" s="33" t="s">
+      <c r="C159" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="D158" s="34" t="s">
+      <c r="D159" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="E158" s="34"/>
-      <c r="F158" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="G158" s="34"/>
-      <c r="H158" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="I158" s="31"/>
-      <c r="J158" s="31"/>
-      <c r="K158" s="34"/>
-      <c r="L158" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="M158" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="N158" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="O158" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="P158" s="55"/>
-    </row>
-    <row r="159" spans="1:16" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B159" s="11" t="s">
-        <v>842</v>
-      </c>
-      <c r="C159" s="30" t="s">
-        <v>832</v>
-      </c>
-      <c r="D159" s="54"/>
-      <c r="E159" s="6" t="s">
-        <v>837</v>
-      </c>
+      <c r="E159" s="34"/>
       <c r="F159" s="35" t="s">
         <v>68</v>
       </c>
+      <c r="G159" s="34"/>
       <c r="H159" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="K159" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="L159" s="6" t="s">
+      <c r="I159" s="31"/>
+      <c r="J159" s="31"/>
+      <c r="K159" s="34"/>
+      <c r="L159" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="M159" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="N159" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="O159" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="M159" s="11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B160" s="11" t="s">
-        <v>842</v>
-      </c>
       <c r="C160" s="30" t="s">
-        <v>834</v>
-      </c>
-      <c r="D160" s="54"/>
+        <v>828</v>
+      </c>
+      <c r="D160" s="53"/>
       <c r="E160" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F160" s="35" t="s">
         <v>68</v>
@@ -9890,10 +9858,10 @@
         <v>64</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="M160" s="11" t="s">
         <v>220</v>
@@ -9901,14 +9869,14 @@
     </row>
     <row r="161" spans="2:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B161" s="11" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C161" s="30" t="s">
+        <v>830</v>
+      </c>
+      <c r="D161" s="53"/>
+      <c r="E161" s="6" t="s">
         <v>833</v>
-      </c>
-      <c r="D161" s="54"/>
-      <c r="E161" s="6" t="s">
-        <v>837</v>
       </c>
       <c r="F161" s="35" t="s">
         <v>68</v>
@@ -9917,10 +9885,10 @@
         <v>64</v>
       </c>
       <c r="K161" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="L161" s="6" t="s">
         <v>836</v>
-      </c>
-      <c r="L161" s="6" t="s">
-        <v>838</v>
       </c>
       <c r="M161" s="11" t="s">
         <v>220</v>
@@ -9928,14 +9896,14 @@
     </row>
     <row r="162" spans="2:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B162" s="11" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C162" s="30" t="s">
-        <v>835</v>
-      </c>
-      <c r="D162" s="54"/>
+        <v>829</v>
+      </c>
+      <c r="D162" s="53"/>
       <c r="E162" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F162" s="35" t="s">
         <v>68</v>
@@ -9944,74 +9912,104 @@
         <v>64</v>
       </c>
       <c r="K162" s="6" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="M162" s="11" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B163" s="11" t="s">
-        <v>843</v>
+        <v>838</v>
+      </c>
+      <c r="C163" s="30" t="s">
+        <v>831</v>
+      </c>
+      <c r="D163" s="53"/>
+      <c r="E163" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="F163" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H163" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="L163" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="M163" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B164" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="C164" s="30" t="s">
+        <v>858</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P163" xr:uid="{374CAC2C-1632-4DD5-8D59-2134E770C16C}"/>
+  <autoFilter ref="A1:O164" xr:uid="{374CAC2C-1632-4DD5-8D59-2134E770C16C}"/>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1" xr:uid="{7FD78E33-6927-4F15-8A75-4BCA99731320}"/>
     <hyperlink ref="L16" r:id="rId2" xr:uid="{2CEFE50E-D59A-4DB5-A6C7-2CCFA70C0F47}"/>
-    <hyperlink ref="K36" r:id="rId3" xr:uid="{668F1EF8-56B0-441C-8FD4-DA76F5A66986}"/>
+    <hyperlink ref="K37" r:id="rId3" xr:uid="{668F1EF8-56B0-441C-8FD4-DA76F5A66986}"/>
     <hyperlink ref="N23" r:id="rId4" xr:uid="{18147931-67CB-40F5-9F45-D656CEF51997}"/>
     <hyperlink ref="N24" r:id="rId5" xr:uid="{96F97762-59C1-4129-95F6-AFFE454FB5E5}"/>
     <hyperlink ref="N25" r:id="rId6" xr:uid="{62841675-8776-4236-A36F-70BFA73ED8A7}"/>
-    <hyperlink ref="N44" r:id="rId7" xr:uid="{8C97B3B3-B031-4061-AC6C-BDB61DD1A012}"/>
-    <hyperlink ref="N45" r:id="rId8" xr:uid="{9826B850-BA99-4DA0-B330-6FBD768AEFEA}"/>
-    <hyperlink ref="N50" r:id="rId9" xr:uid="{36396F66-6A06-4BD3-A1F9-A1AC087F45D0}"/>
-    <hyperlink ref="N52" r:id="rId10" xr:uid="{67FCFBD4-07AB-4F02-9516-2DD85CE91D49}"/>
-    <hyperlink ref="N55" r:id="rId11" xr:uid="{1EFA0127-8D9F-4F42-8036-E87EA98187A0}"/>
-    <hyperlink ref="N56" r:id="rId12" xr:uid="{9938B93E-B614-4962-BB12-BB567D5BA699}"/>
-    <hyperlink ref="N57" r:id="rId13" xr:uid="{D8FE8AD4-09BF-4BBB-8562-F10360DF2F41}"/>
-    <hyperlink ref="N58" r:id="rId14" xr:uid="{357B290B-8838-475E-8B97-B93FEAE1BEC2}"/>
-    <hyperlink ref="N61" r:id="rId15" xr:uid="{8ED84B93-4045-41B2-A5A8-3DA4CFDB104A}"/>
-    <hyperlink ref="N62" r:id="rId16" xr:uid="{996D4DD9-EACA-4FAF-9DC1-97563A4E203F}"/>
-    <hyperlink ref="N63" r:id="rId17" xr:uid="{D9189AC0-A20D-49D4-9F86-E6A35AD1D257}"/>
-    <hyperlink ref="N64" r:id="rId18" xr:uid="{D5F31C46-F52C-4177-A643-FDA4B7A6A851}"/>
-    <hyperlink ref="N65" r:id="rId19" xr:uid="{9F68A199-BBF1-4A5F-86B9-471454328DCF}"/>
-    <hyperlink ref="N66" r:id="rId20" xr:uid="{91A4D4D5-1CC0-4101-A9FA-D5616D691A20}"/>
-    <hyperlink ref="N67" r:id="rId21" xr:uid="{948E6CD1-A6DA-4E4D-810B-4782B0210C4D}"/>
-    <hyperlink ref="N68" r:id="rId22" xr:uid="{A26890B1-CAAE-467B-926C-A40B3E24319A}"/>
-    <hyperlink ref="N69" r:id="rId23" xr:uid="{B0F0A35B-E386-4FF2-9BE9-6E308606E9D9}"/>
-    <hyperlink ref="N70" r:id="rId24" xr:uid="{9F6B59CD-7B06-4BFE-A6DE-0284F63E164B}"/>
-    <hyperlink ref="N71" r:id="rId25" xr:uid="{E8A3CD58-A844-4362-869D-26A4D188C17A}"/>
-    <hyperlink ref="N72" r:id="rId26" xr:uid="{0BC4BFD2-50E5-4210-9C6C-D2DD497F6FCF}"/>
-    <hyperlink ref="N73" r:id="rId27" xr:uid="{8E6F7099-22BB-4516-84D4-79FD642290E1}"/>
-    <hyperlink ref="N74" r:id="rId28" xr:uid="{97C147DB-1E82-43CD-9A4C-7E318A6AEC40}"/>
-    <hyperlink ref="N75" r:id="rId29" xr:uid="{ABB064D3-8141-4273-966B-5D643A2F6EA5}"/>
-    <hyperlink ref="N76" r:id="rId30" xr:uid="{7F3E044D-1BC5-4C4C-A85B-54C7F42F6771}"/>
-    <hyperlink ref="N98" r:id="rId31" xr:uid="{28014383-C7B6-463C-8B01-AA065C25A4E5}"/>
-    <hyperlink ref="N99" r:id="rId32" xr:uid="{2F6EBA5A-F487-4293-8309-5F8FEC4F7361}"/>
-    <hyperlink ref="N100" r:id="rId33" xr:uid="{1C85334C-1895-4625-B4F6-B89BAA00FCA0}"/>
-    <hyperlink ref="N111" r:id="rId34" xr:uid="{583702D4-D50A-42B9-ADF4-86D4CDAED058}"/>
-    <hyperlink ref="N112" r:id="rId35" xr:uid="{4666FF26-8921-4930-A999-B4D79D8B1BE2}"/>
-    <hyperlink ref="N113" r:id="rId36" xr:uid="{1919902E-4C24-49B0-94D8-043B4DA350C8}"/>
-    <hyperlink ref="N115" r:id="rId37" xr:uid="{E6A02095-322F-43DE-97EC-030B11159D1E}"/>
-    <hyperlink ref="N116" r:id="rId38" xr:uid="{F16972C6-48E6-4744-85AC-9319AD11E2E0}"/>
-    <hyperlink ref="N117" r:id="rId39" xr:uid="{0BAC70B3-7A64-4AD7-BF3D-48B5EE214F4E}"/>
-    <hyperlink ref="N118" r:id="rId40" xr:uid="{6913768C-6727-41F6-B8B6-482ACD5CE40D}"/>
-    <hyperlink ref="N120" r:id="rId41" xr:uid="{716756AB-E635-4250-88B3-FBCC9195D77B}"/>
-    <hyperlink ref="N121" r:id="rId42" xr:uid="{CED9821E-95F1-45F7-849B-65127B5451F3}"/>
-    <hyperlink ref="N126" r:id="rId43" xr:uid="{7358A7E2-F166-4D71-82BB-3540F41B89B1}"/>
-    <hyperlink ref="N127" r:id="rId44" xr:uid="{ED5E9491-F490-420E-ACF0-2B93CE3EF63D}"/>
-    <hyperlink ref="N102" r:id="rId45" xr:uid="{77527673-5684-4821-A2EE-A18807C74F67}"/>
-    <hyperlink ref="N103" r:id="rId46" xr:uid="{2C2E6B9A-027F-4E26-B373-892C413A600B}"/>
-    <hyperlink ref="N104" r:id="rId47" xr:uid="{710B3BAC-88A9-407C-B619-6F8817C25EA4}"/>
-    <hyperlink ref="N145" r:id="rId48" xr:uid="{E5BF68F8-25B5-4B20-B423-F162D2CA880D}"/>
-    <hyperlink ref="N148" r:id="rId49" xr:uid="{3AF5F976-AC87-47D7-B09A-40CF0376A825}"/>
-    <hyperlink ref="N146" r:id="rId50" xr:uid="{993DF5C1-61CC-4311-9A07-8D9E681BA027}"/>
-    <hyperlink ref="N147" r:id="rId51" xr:uid="{D0009EBC-E1C9-4693-96F9-56F4AED5671A}"/>
+    <hyperlink ref="N45" r:id="rId7" xr:uid="{8C97B3B3-B031-4061-AC6C-BDB61DD1A012}"/>
+    <hyperlink ref="N46" r:id="rId8" xr:uid="{9826B850-BA99-4DA0-B330-6FBD768AEFEA}"/>
+    <hyperlink ref="N51" r:id="rId9" xr:uid="{36396F66-6A06-4BD3-A1F9-A1AC087F45D0}"/>
+    <hyperlink ref="N53" r:id="rId10" xr:uid="{67FCFBD4-07AB-4F02-9516-2DD85CE91D49}"/>
+    <hyperlink ref="N56" r:id="rId11" xr:uid="{1EFA0127-8D9F-4F42-8036-E87EA98187A0}"/>
+    <hyperlink ref="N57" r:id="rId12" xr:uid="{9938B93E-B614-4962-BB12-BB567D5BA699}"/>
+    <hyperlink ref="N58" r:id="rId13" xr:uid="{D8FE8AD4-09BF-4BBB-8562-F10360DF2F41}"/>
+    <hyperlink ref="N59" r:id="rId14" xr:uid="{357B290B-8838-475E-8B97-B93FEAE1BEC2}"/>
+    <hyperlink ref="N62" r:id="rId15" xr:uid="{8ED84B93-4045-41B2-A5A8-3DA4CFDB104A}"/>
+    <hyperlink ref="N63" r:id="rId16" xr:uid="{996D4DD9-EACA-4FAF-9DC1-97563A4E203F}"/>
+    <hyperlink ref="N64" r:id="rId17" xr:uid="{D9189AC0-A20D-49D4-9F86-E6A35AD1D257}"/>
+    <hyperlink ref="N65" r:id="rId18" xr:uid="{D5F31C46-F52C-4177-A643-FDA4B7A6A851}"/>
+    <hyperlink ref="N66" r:id="rId19" xr:uid="{9F68A199-BBF1-4A5F-86B9-471454328DCF}"/>
+    <hyperlink ref="N67" r:id="rId20" xr:uid="{91A4D4D5-1CC0-4101-A9FA-D5616D691A20}"/>
+    <hyperlink ref="N68" r:id="rId21" xr:uid="{948E6CD1-A6DA-4E4D-810B-4782B0210C4D}"/>
+    <hyperlink ref="N69" r:id="rId22" xr:uid="{A26890B1-CAAE-467B-926C-A40B3E24319A}"/>
+    <hyperlink ref="N70" r:id="rId23" xr:uid="{B0F0A35B-E386-4FF2-9BE9-6E308606E9D9}"/>
+    <hyperlink ref="N71" r:id="rId24" xr:uid="{9F6B59CD-7B06-4BFE-A6DE-0284F63E164B}"/>
+    <hyperlink ref="N72" r:id="rId25" xr:uid="{E8A3CD58-A844-4362-869D-26A4D188C17A}"/>
+    <hyperlink ref="N73" r:id="rId26" xr:uid="{0BC4BFD2-50E5-4210-9C6C-D2DD497F6FCF}"/>
+    <hyperlink ref="N74" r:id="rId27" xr:uid="{8E6F7099-22BB-4516-84D4-79FD642290E1}"/>
+    <hyperlink ref="N75" r:id="rId28" xr:uid="{97C147DB-1E82-43CD-9A4C-7E318A6AEC40}"/>
+    <hyperlink ref="N76" r:id="rId29" xr:uid="{ABB064D3-8141-4273-966B-5D643A2F6EA5}"/>
+    <hyperlink ref="N77" r:id="rId30" xr:uid="{7F3E044D-1BC5-4C4C-A85B-54C7F42F6771}"/>
+    <hyperlink ref="N99" r:id="rId31" xr:uid="{28014383-C7B6-463C-8B01-AA065C25A4E5}"/>
+    <hyperlink ref="N100" r:id="rId32" xr:uid="{2F6EBA5A-F487-4293-8309-5F8FEC4F7361}"/>
+    <hyperlink ref="N101" r:id="rId33" xr:uid="{1C85334C-1895-4625-B4F6-B89BAA00FCA0}"/>
+    <hyperlink ref="N112" r:id="rId34" xr:uid="{583702D4-D50A-42B9-ADF4-86D4CDAED058}"/>
+    <hyperlink ref="N113" r:id="rId35" xr:uid="{4666FF26-8921-4930-A999-B4D79D8B1BE2}"/>
+    <hyperlink ref="N114" r:id="rId36" xr:uid="{1919902E-4C24-49B0-94D8-043B4DA350C8}"/>
+    <hyperlink ref="N116" r:id="rId37" xr:uid="{E6A02095-322F-43DE-97EC-030B11159D1E}"/>
+    <hyperlink ref="N117" r:id="rId38" xr:uid="{F16972C6-48E6-4744-85AC-9319AD11E2E0}"/>
+    <hyperlink ref="N118" r:id="rId39" xr:uid="{0BAC70B3-7A64-4AD7-BF3D-48B5EE214F4E}"/>
+    <hyperlink ref="N119" r:id="rId40" xr:uid="{6913768C-6727-41F6-B8B6-482ACD5CE40D}"/>
+    <hyperlink ref="N121" r:id="rId41" xr:uid="{716756AB-E635-4250-88B3-FBCC9195D77B}"/>
+    <hyperlink ref="N122" r:id="rId42" xr:uid="{CED9821E-95F1-45F7-849B-65127B5451F3}"/>
+    <hyperlink ref="N127" r:id="rId43" xr:uid="{7358A7E2-F166-4D71-82BB-3540F41B89B1}"/>
+    <hyperlink ref="N128" r:id="rId44" xr:uid="{ED5E9491-F490-420E-ACF0-2B93CE3EF63D}"/>
+    <hyperlink ref="N103" r:id="rId45" xr:uid="{77527673-5684-4821-A2EE-A18807C74F67}"/>
+    <hyperlink ref="N104" r:id="rId46" xr:uid="{2C2E6B9A-027F-4E26-B373-892C413A600B}"/>
+    <hyperlink ref="N105" r:id="rId47" xr:uid="{710B3BAC-88A9-407C-B619-6F8817C25EA4}"/>
+    <hyperlink ref="N146" r:id="rId48" xr:uid="{E5BF68F8-25B5-4B20-B423-F162D2CA880D}"/>
+    <hyperlink ref="N149" r:id="rId49" xr:uid="{3AF5F976-AC87-47D7-B09A-40CF0376A825}"/>
+    <hyperlink ref="N147" r:id="rId50" xr:uid="{993DF5C1-61CC-4311-9A07-8D9E681BA027}"/>
+    <hyperlink ref="N148" r:id="rId51" xr:uid="{D0009EBC-E1C9-4693-96F9-56F4AED5671A}"/>
     <hyperlink ref="N6" r:id="rId52" xr:uid="{6D24AEEA-6B6F-4930-B3D2-B90CF33AE3E8}"/>
     <hyperlink ref="N5" r:id="rId53" xr:uid="{85B8D4EB-55EF-4C26-90A7-6C95D2FED8E0}"/>
     <hyperlink ref="N3" r:id="rId54" location="dwc_recordedByID" xr:uid="{D2798DAE-4753-4625-B369-A6C4C501C9BC}"/>
@@ -10021,25 +10019,23 @@
     <hyperlink ref="N12" r:id="rId58" xr:uid="{AC676A2F-6001-4E6F-9FD6-2E34E1D08EFE}"/>
     <hyperlink ref="N13" r:id="rId59" xr:uid="{FDF54E03-D185-4C65-B07C-FBA8BBD7D708}"/>
     <hyperlink ref="N14" r:id="rId60" xr:uid="{12402D92-AD8B-4545-B512-C0DD6135CF28}"/>
-    <hyperlink ref="N158" r:id="rId61" xr:uid="{6E80ED66-DC86-4033-BAD1-10200C302FB1}"/>
+    <hyperlink ref="N159" r:id="rId61" xr:uid="{6E80ED66-DC86-4033-BAD1-10200C302FB1}"/>
     <hyperlink ref="N17" r:id="rId62" xr:uid="{C80CFE62-F3BD-4D26-9673-0139FB0AB03C}"/>
     <hyperlink ref="N18" r:id="rId63" xr:uid="{AC677A1E-B6B2-474B-99BD-4B59D2935A96}"/>
     <hyperlink ref="N19" r:id="rId64" xr:uid="{73512B7D-A665-45A4-9E3B-C33CF57388FD}"/>
     <hyperlink ref="N20" r:id="rId65" xr:uid="{DBF85759-9ED1-4A10-BF20-6B3C65836DAF}"/>
     <hyperlink ref="N21" r:id="rId66" xr:uid="{AF4FCCD9-689B-4F22-A750-9C6FDB0ADCC5}"/>
     <hyperlink ref="N22" r:id="rId67" xr:uid="{A87578AB-8A62-4C9E-BAD6-3692F1CF3C7E}"/>
-    <hyperlink ref="N46" r:id="rId68" xr:uid="{D9AA459A-844E-41D2-A0E0-D3E50C59CA06}"/>
-    <hyperlink ref="N137" r:id="rId69" xr:uid="{916FC72D-83B8-4C24-A55E-9487FFDD18A3}"/>
-    <hyperlink ref="N105" r:id="rId70" xr:uid="{24D47E0F-0E0A-45D3-9FF5-44F3F556451F}"/>
-    <hyperlink ref="N108" r:id="rId71" xr:uid="{60EB85D8-DF5C-4D9C-8469-9E585D6CE8CC}"/>
-    <hyperlink ref="N106" r:id="rId72" xr:uid="{EEC3BD52-3D02-4466-82EB-6A0D09FC1F62}"/>
-    <hyperlink ref="N107" r:id="rId73" xr:uid="{223D6FDD-E1DE-4638-8D45-6E2A194233A2}"/>
-    <hyperlink ref="N119" r:id="rId74" xr:uid="{2EB2A753-1484-45AC-A18D-332A9D1ED64F}"/>
-    <hyperlink ref="K87" r:id="rId75" xr:uid="{4930E157-E779-4B01-983D-669FC0AD243C}"/>
-    <hyperlink ref="P3" r:id="rId76" xr:uid="{EF9474F3-A786-4ACD-894E-C206D926AB25}"/>
-    <hyperlink ref="P4" r:id="rId77" xr:uid="{C46818EE-4EF9-436F-82FC-1A464D5277AD}"/>
-    <hyperlink ref="N48" r:id="rId78" xr:uid="{5D12BC62-66F1-40DE-B1B0-D55DD70B292F}"/>
-    <hyperlink ref="N49" r:id="rId79" xr:uid="{8D8F12FF-32CC-4B11-9BDD-4BEF084F0E57}"/>
+    <hyperlink ref="N47" r:id="rId68" xr:uid="{D9AA459A-844E-41D2-A0E0-D3E50C59CA06}"/>
+    <hyperlink ref="N138" r:id="rId69" xr:uid="{916FC72D-83B8-4C24-A55E-9487FFDD18A3}"/>
+    <hyperlink ref="N106" r:id="rId70" xr:uid="{24D47E0F-0E0A-45D3-9FF5-44F3F556451F}"/>
+    <hyperlink ref="N109" r:id="rId71" xr:uid="{60EB85D8-DF5C-4D9C-8469-9E585D6CE8CC}"/>
+    <hyperlink ref="N107" r:id="rId72" xr:uid="{EEC3BD52-3D02-4466-82EB-6A0D09FC1F62}"/>
+    <hyperlink ref="N108" r:id="rId73" xr:uid="{223D6FDD-E1DE-4638-8D45-6E2A194233A2}"/>
+    <hyperlink ref="N120" r:id="rId74" xr:uid="{2EB2A753-1484-45AC-A18D-332A9D1ED64F}"/>
+    <hyperlink ref="K88" r:id="rId75" xr:uid="{4930E157-E779-4B01-983D-669FC0AD243C}"/>
+    <hyperlink ref="N49" r:id="rId76" xr:uid="{5D12BC62-66F1-40DE-B1B0-D55DD70B292F}"/>
+    <hyperlink ref="N50" r:id="rId77" xr:uid="{8D8F12FF-32CC-4B11-9BDD-4BEF084F0E57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10521,7 +10517,7 @@
         <v>50</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
@@ -10960,7 +10956,7 @@
         <v>527</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="102" customHeight="1" x14ac:dyDescent="0.3">
@@ -10984,7 +10980,7 @@
       </c>
       <c r="N28" s="6"/>
       <c r="P28" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -11065,7 +11061,7 @@
       </c>
       <c r="N31" s="6"/>
       <c r="P31" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="144" x14ac:dyDescent="0.3">
@@ -11088,7 +11084,7 @@
       </c>
       <c r="N32" s="6"/>
       <c r="P32" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
@@ -11096,7 +11092,7 @@
         <v>162</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -11108,7 +11104,7 @@
       </c>
       <c r="N33" s="6"/>
       <c r="P33" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
@@ -11137,10 +11133,10 @@
         <v>162</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F35" s="14"/>
       <c r="K35" s="6" t="s">
@@ -11151,7 +11147,7 @@
       </c>
       <c r="N35" s="6"/>
       <c r="P35" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -11184,7 +11180,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B37" s="17" t="s">
         <v>162</v>
       </c>
@@ -11207,7 +11203,7 @@
         <v>605</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>605</v>
+        <v>850</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -11236,7 +11232,7 @@
         <v>605</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
@@ -11247,10 +11243,10 @@
         <v>173</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>68</v>
@@ -11266,7 +11262,7 @@
       </c>
       <c r="N39" s="6"/>
       <c r="P39" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="345.6" x14ac:dyDescent="0.3">
@@ -11310,10 +11306,10 @@
         <v>190</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>68</v>
@@ -11329,7 +11325,7 @@
       </c>
       <c r="N41" s="6"/>
       <c r="P41" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="72" x14ac:dyDescent="0.3">
@@ -11337,7 +11333,7 @@
         <v>162</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>68</v>
@@ -11347,7 +11343,7 @@
       </c>
       <c r="N42" s="6"/>
       <c r="P42" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -11379,13 +11375,13 @@
         <v>162</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D44" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>679</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>680</v>
       </c>
       <c r="F44" s="14" t="s">
         <v>82</v>
@@ -11401,7 +11397,7 @@
       </c>
       <c r="N44" s="6"/>
       <c r="P44" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -11409,7 +11405,7 @@
         <v>162</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>82</v>
@@ -11419,7 +11415,7 @@
       </c>
       <c r="N45" s="6"/>
       <c r="P45" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -11427,20 +11423,20 @@
         <v>162</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F46" s="14" t="s">
         <v>82</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N46" s="6"/>
       <c r="P46" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -11448,7 +11444,7 @@
         <v>162</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>82</v>
@@ -11458,7 +11454,7 @@
       </c>
       <c r="N47" s="6"/>
       <c r="P47" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -11485,7 +11481,7 @@
       </c>
       <c r="N48" s="6"/>
       <c r="P48" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12371,7 +12367,7 @@
         <v>551</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -12987,23 +12983,23 @@
         <v>211</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>84</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M99" s="11" t="s">
         <v>220</v>
       </c>
       <c r="N99" s="6"/>
       <c r="P99" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -13111,7 +13107,7 @@
         <v>554</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -13248,7 +13244,7 @@
         <v>558</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -13401,7 +13397,7 @@
       </c>
       <c r="N111" s="6"/>
       <c r="P111" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
@@ -13461,7 +13457,7 @@
         <v>561</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="409.6" x14ac:dyDescent="0.3">
@@ -13493,7 +13489,7 @@
         <v>562</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -13645,7 +13641,7 @@
         <v>524</v>
       </c>
       <c r="P119" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
@@ -13674,7 +13670,7 @@
         <v>525</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -14535,7 +14531,7 @@
       </c>
       <c r="N151" s="6"/>
       <c r="P151" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
@@ -14743,7 +14739,7 @@
         <v>50</v>
       </c>
       <c r="P160" s="34" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -14862,7 +14858,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -14890,7 +14886,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -14921,7 +14917,7 @@
         <v>386</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>411</v>
@@ -14940,13 +14936,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -15020,13 +15016,13 @@
     </row>
     <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
